--- a/docs/data/jp/xlsx/8119.xlsx
+++ b/docs/data/jp/xlsx/8119.xlsx
@@ -2119,7 +2119,7 @@
     <row r="7">
       <c r="A7" s="18" t="inlineStr">
         <is>
-          <t>Furniture And Houseware Reportable Segments</t>
+          <t>가구·가정용품 사업</t>
         </is>
       </c>
       <c r="B7" s="10" t="n"/>
@@ -2401,7 +2401,7 @@
     <row r="10">
       <c r="A10" s="18" t="inlineStr">
         <is>
-          <t>Fashion Accessories Reportable Segments</t>
+          <t>패션 잡화 사업</t>
         </is>
       </c>
       <c r="B10" s="10" t="n"/>
@@ -2683,7 +2683,7 @@
     <row r="13">
       <c r="A13" s="18" t="inlineStr">
         <is>
-          <t>Home Appliance Reportable Segments</t>
+          <t>가전 사업</t>
         </is>
       </c>
       <c r="B13" s="10" t="n"/>
@@ -8633,7 +8633,7 @@
     <row r="100">
       <c r="A100" s="18" t="inlineStr">
         <is>
-          <t>General And Administrative Expenses SGA</t>
+          <t>일반관리비</t>
         </is>
       </c>
       <c r="C100" s="20" t="n">
@@ -9920,7 +9920,7 @@
     <row r="123">
       <c r="A123" s="18" t="inlineStr">
         <is>
-          <t>Gain On Refund Of Deposits Of Golfclub Membership EI</t>
+          <t>골프 회원권 예탁금 반환 이익</t>
         </is>
       </c>
       <c r="E123" s="20" t="n">
@@ -10296,7 +10296,7 @@
     <row r="133">
       <c r="A133" s="18" t="inlineStr">
         <is>
-          <t>Loss On Cancellation Of Contract2EL</t>
+          <t>계약 해제 손실</t>
         </is>
       </c>
       <c r="D133" s="20" t="n">
@@ -12051,7 +12051,7 @@
     <row r="163">
       <c r="A163" s="18" t="inlineStr">
         <is>
-          <t>부문 · 외부 고객 매출</t>
+          <t>가구·가정용품 사업 · 외부 고객 매출</t>
         </is>
       </c>
       <c r="C163" s="20" t="n">
@@ -12159,7 +12159,7 @@
     <row r="165">
       <c r="A165" s="18" t="inlineStr">
         <is>
-          <t>부문 · 외부 고객 매출</t>
+          <t>패션 잡화 사업 · 외부 고객 매출</t>
         </is>
       </c>
       <c r="C165" s="20" t="n">
@@ -12267,7 +12267,7 @@
     <row r="167">
       <c r="A167" s="18" t="inlineStr">
         <is>
-          <t>부문 · 외부 고객 매출</t>
+          <t>가전 사업 · 외부 고객 매출</t>
         </is>
       </c>
       <c r="C167" s="20" t="n">
@@ -12859,7 +12859,7 @@
     <row r="178">
       <c r="A178" s="18" t="inlineStr">
         <is>
-          <t>부문 · 부문 간 내부매출·대체</t>
+          <t>가구·가정용품 사업 · 부문 간 내부매출·대체</t>
         </is>
       </c>
       <c r="C178" s="20" t="n">
@@ -12911,7 +12911,7 @@
     <row r="179">
       <c r="A179" s="18" t="inlineStr">
         <is>
-          <t>부문 · 부문 간 내부매출·대체</t>
+          <t>패션 잡화 사업 · 부문 간 내부매출·대체</t>
         </is>
       </c>
       <c r="C179" s="20" t="n">
@@ -12963,7 +12963,7 @@
     <row r="180">
       <c r="A180" s="18" t="inlineStr">
         <is>
-          <t>부문 · 부문 간 내부매출·대체</t>
+          <t>가전 사업 · 부문 간 내부매출·대체</t>
         </is>
       </c>
       <c r="C180" s="20" t="n">
@@ -13275,7 +13275,7 @@
     <row r="186">
       <c r="A186" s="18" t="inlineStr">
         <is>
-          <t>부문 · 계</t>
+          <t>가구·가정용품 사업 · 계</t>
         </is>
       </c>
       <c r="C186" s="20" t="n">
@@ -13383,7 +13383,7 @@
     <row r="188">
       <c r="A188" s="18" t="inlineStr">
         <is>
-          <t>부문 · 계</t>
+          <t>패션 잡화 사업 · 계</t>
         </is>
       </c>
       <c r="C188" s="20" t="n">
@@ -13491,7 +13491,7 @@
     <row r="190">
       <c r="A190" s="18" t="inlineStr">
         <is>
-          <t>부문 · 계</t>
+          <t>가전 사업 · 계</t>
         </is>
       </c>
       <c r="C190" s="20" t="n">
@@ -14083,7 +14083,7 @@
     <row r="201">
       <c r="A201" s="18" t="inlineStr">
         <is>
-          <t>부문 · 부문 이익(손실)</t>
+          <t>가구·가정용품 사업 · 부문 이익(손실)</t>
         </is>
       </c>
       <c r="C201" s="20" t="n">
@@ -14263,7 +14263,7 @@
     <row r="204">
       <c r="A204" s="18" t="inlineStr">
         <is>
-          <t>부문 · 부문 이익(손실)</t>
+          <t>패션 잡화 사업 · 부문 이익(손실)</t>
         </is>
       </c>
       <c r="C204" s="20" t="n">
@@ -14443,7 +14443,7 @@
     <row r="207">
       <c r="A207" s="18" t="inlineStr">
         <is>
-          <t>부문 · 부문 이익(손실)</t>
+          <t>가전 사업 · 부문 이익(손실)</t>
         </is>
       </c>
       <c r="C207" s="20" t="n">
@@ -16116,7 +16116,7 @@
     <row r="236">
       <c r="A236" s="18" t="inlineStr">
         <is>
-          <t>Gain On Refund Of Deposits Of Golfclub Membership Ope CF</t>
+          <t>골프 회원권 예탁금 반환 이익</t>
         </is>
       </c>
       <c r="F236" s="20" t="n">
@@ -16283,7 +16283,7 @@
     <row r="241">
       <c r="A241" s="18" t="inlineStr">
         <is>
-          <t>Provision For Loss On Voluntary Recall Affairs Ope CF</t>
+          <t>상품 자율 회수 관련 손실 충당금 전입액</t>
         </is>
       </c>
       <c r="O241" s="20" t="n">
@@ -16538,7 +16538,7 @@
     <row r="247">
       <c r="A247" s="18" t="inlineStr">
         <is>
-          <t>Provision For Loss On Fire Disaster Affairs Ope CF</t>
+          <t>화재 관련 손실 충당금 전입액</t>
         </is>
       </c>
       <c r="O247" s="20" t="n">
@@ -17585,7 +17585,7 @@
     <row r="271">
       <c r="A271" s="18" t="inlineStr">
         <is>
-          <t>Decrease Increase In Deposits For Treasury Shares Fin CF</t>
+          <t>자기주식 취득용 예탁금 증감액</t>
         </is>
       </c>
       <c r="F271" s="20" t="n">
@@ -18049,7 +18049,7 @@
     <row r="282">
       <c r="A282" s="18" t="inlineStr">
         <is>
-          <t>Increase Decrease In Cash And Cash Equivalents Resulting From Merger Of Subsidiaries CCE</t>
+          <t>연결 자회사 합병에 따른 현금성자산 증감액(△는 감소)</t>
         </is>
       </c>
       <c r="D282" s="20" t="n">
